--- a/PeerReview/Flooring Mastery Peer Review Steven.xlsx
+++ b/PeerReview/Flooring Mastery Peer Review Steven.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steven\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83187D33-19C0-4CCF-A79E-F12B80FBE19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D4A192-4743-412E-AD69-FB098D9B855A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
